--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.2</v>
+        <v>0.2424242424242424</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.2765957446808511</v>
+        <v>0.3237410071942446</v>
       </c>
       <c r="D2">
-        <v>0.8360655737704918</v>
+        <v>0.7966101694915254</v>
       </c>
       <c r="E2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
